--- a/data/trans_camb/IP16A03-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>0.4821833664014318</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.07541439259563643</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.098736850122514</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.488611062180979</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.2744683125323092</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.2763964397678094</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-1.30304231103078</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.527423781559104</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.646996537958929</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.996725067505931</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-1.401542666989371</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-1.410616698755951</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>1.916253061345096</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.16195703300856</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.08228271168657576</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.678291852191408</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.7958398744689907</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1.692897607909065</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.4861832758339188</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.07603998601363382</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.7897247009477024</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.3511925762001946</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2313453687927887</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2329705593375943</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,18 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.7950390916434542</v>
+      </c>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="6" t="inlineStr"/>
       <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-0.7700187830601405</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +724,18 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>7.531148717296048</v>
+      </c>
       <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>1.74295372142947</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>3.171150883676489</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +748,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-0.7285231134930016</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.2951074627932671</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.4750680268140642</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.5878342180792127</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.6025340295856481</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.4390151094524565</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +774,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-2.432468110466175</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.707218828086214</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.921962787928507</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.91815452824131</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-1.546419715299086</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-1.358823925369898</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +800,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.7466478388470816</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5498421705535723</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.4260705781812298</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.06711659868440337</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.2713658782964577</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +826,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.4050763212965679</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.5096086677499654</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.6305737196042376</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.7255418047680553</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.5286403741405672</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -809,11 +856,10 @@
       <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="6" t="inlineStr"/>
       <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-1</v>
+      </c>
       <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -826,11 +872,10 @@
       <c r="D15" s="6" t="inlineStr"/>
       <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>1.360371950429765</v>
+      </c>
       <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +888,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>0.9087236051995684</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.3944897842013909</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.02236836334547311</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.4769121371958197</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.4346649851829211</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.001001463951296952</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +914,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-0.4113902934943554</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.8069794261302103</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.440492689074366</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.650639327659276</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.5304196972234262</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.9479013754100288</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +940,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>2.928389189988921</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.67288571496714</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.916123181218364</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.578895493676022</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.7650576588093692</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +966,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>2.219344241657783</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.9634487603828714</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.04690248287031679</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.9819728778271051</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.002262456079551291</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -917,9 +998,6 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -934,9 +1012,6 @@
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1024,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-1.371957797524678</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.9677918398686591</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.5543810818244571</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.2767458856182479</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.000404971204053</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.38619890842704</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1050,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-4.174362215707623</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.979552241262667</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.387868743460768</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-1.127115923035803</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-2.765560758138043</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-1.957723026524157</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1076,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.41054288684045</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.295882267890003</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.2477935813284373</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.6695605433463792</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1102,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.7054093366536305</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.4991979248416678</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.386042572301719</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1022,10 +1133,9 @@
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="n">
+        <v>-0.9495289490070766</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1040,9 +1150,6 @@
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1162,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>0.005097938154850767</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.2146035798600602</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.6047261947235338</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-0.5181625732157698</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.2909345420357518</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-0.3589797415999071</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1188,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-0.8902600067959527</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-1.017896328294678</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-1.379940387956906</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-1.221657044411646</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.9188639156874392</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-0.9364314215421826</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1214,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.8360030241397445</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.4700033775125601</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.001057130711817396</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.1763140865193309</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.1845367762665711</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.123861608955976</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1240,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.006100480764462657</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.2568067660207711</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.6384470866565242</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.5470564830341088</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.3268504923423422</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.4032958907589526</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.6751052400021643</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.7681091602159413</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.9299293306414622</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.8843772554582573</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.7159238960951415</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.7587912689032205</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>2.13761381748093</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1.292591601694724</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.1852222322425695</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.5650004438338806</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.3472492447760887</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.2779748016300177</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1320,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
